--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_26-12-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_26-12-2025.xlsx
@@ -289,7 +289,7 @@
     <t>£20.51</t>
   </si>
   <si>
-    <t>POA or OOS</t>
+    <t>£20.16</t>
   </si>
   <si>
     <t>£23.58</t>
@@ -298,6 +298,9 @@
     <t>£25.44</t>
   </si>
   <si>
+    <t>£30.37</t>
+  </si>
+  <si>
     <t>£37.48</t>
   </si>
   <si>
@@ -343,7 +346,7 @@
     <t>£62.80</t>
   </si>
   <si>
-    <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+    <t>£71.35</t>
   </si>
   <si>
     <t>£75.80</t>
@@ -500,9 +503,6 @@
   </si>
   <si>
     <t>£67.76</t>
-  </si>
-  <si>
-    <t>Price Not Found</t>
   </si>
 </sst>
 </file>
@@ -942,25 +942,25 @@
         <v>46</v>
       </c>
       <c r="J2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N2" t="s">
         <v>56</v>
       </c>
       <c r="O2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -992,25 +992,25 @@
         <v>86</v>
       </c>
       <c r="J3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K3" t="s">
         <v>77</v>
       </c>
       <c r="L3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N3" t="s">
         <v>56</v>
       </c>
       <c r="O3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1042,25 +1042,25 @@
         <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K4" t="s">
         <v>78</v>
       </c>
       <c r="L4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N4" t="s">
         <v>56</v>
       </c>
       <c r="O4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1092,25 +1092,25 @@
         <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K5" t="s">
         <v>49</v>
       </c>
       <c r="L5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N5" t="s">
         <v>56</v>
       </c>
       <c r="O5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1142,25 +1142,25 @@
         <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s">
         <v>50</v>
       </c>
       <c r="L6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N6" t="s">
         <v>56</v>
       </c>
       <c r="O6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P6" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1192,25 +1192,25 @@
         <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N7" t="s">
         <v>56</v>
       </c>
       <c r="O7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1242,25 +1242,25 @@
         <v>91</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
         <v>79</v>
       </c>
       <c r="L8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N8" t="s">
         <v>56</v>
       </c>
       <c r="O8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1292,25 +1292,25 @@
         <v>92</v>
       </c>
       <c r="J9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K9" t="s">
         <v>80</v>
       </c>
       <c r="L9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N9" t="s">
         <v>56</v>
       </c>
       <c r="O9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P9" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1342,25 +1342,25 @@
         <v>93</v>
       </c>
       <c r="J10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K10" t="s">
         <v>54</v>
       </c>
       <c r="L10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s">
         <v>56</v>
       </c>
       <c r="O10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P10" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1392,25 +1392,25 @@
         <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N11" t="s">
         <v>56</v>
       </c>
       <c r="O11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P11" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1442,13 +1442,13 @@
         <v>83</v>
       </c>
       <c r="J12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K12" t="s">
         <v>56</v>
       </c>
       <c r="L12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M12" t="s">
         <v>56</v>
@@ -1457,7 +1457,7 @@
         <v>56</v>
       </c>
       <c r="O12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s">
         <v>56</v>
@@ -1489,28 +1489,28 @@
         <v>57</v>
       </c>
       <c r="I13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N13" t="s">
         <v>56</v>
       </c>
       <c r="O13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1539,25 +1539,25 @@
         <v>84</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K14" t="s">
         <v>56</v>
       </c>
       <c r="L14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N14" t="s">
         <v>56</v>
       </c>
       <c r="O14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P14" t="s">
         <v>56</v>
@@ -1589,25 +1589,25 @@
         <v>85</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s">
         <v>56</v>
       </c>
       <c r="O15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P15" t="s">
         <v>56</v>
@@ -1639,28 +1639,28 @@
         <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N16" t="s">
         <v>56</v>
       </c>
       <c r="O16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P16" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
